--- a/Einzelabend_14.09.2026.xlsx
+++ b/Einzelabend_14.09.2026.xlsx
@@ -893,13 +893,13 @@
         <v>Pünkt</v>
       </c>
       <c r="C23">
-        <v>5500</v>
+        <v>5491</v>
       </c>
       <c r="E23">
         <v>6885</v>
       </c>
       <c r="H23">
-        <v>-1385</v>
+        <v>-1394</v>
       </c>
     </row>
     <row r="24">
@@ -907,13 +907,13 @@
         <v>Runde 1</v>
       </c>
       <c r="C24">
-        <v>2709</v>
+        <v>2700</v>
       </c>
       <c r="E24">
         <v>3665</v>
       </c>
       <c r="H24">
-        <v>-956</v>
+        <v>-965</v>
       </c>
     </row>
     <row r="25">
@@ -1170,13 +1170,13 @@
         <v>Anteil Wiise an Total</v>
       </c>
       <c r="C38">
-        <v>0.14545454545454545</v>
+        <v>0.145692952103442</v>
       </c>
       <c r="E38">
         <v>0.23093681917211328</v>
       </c>
       <c r="H38">
-        <v>-0.3701543739279588</v>
+        <v>-0.36912202815585027</v>
       </c>
     </row>
     <row r="40">

--- a/Einzelabend_14.09.2026.xlsx
+++ b/Einzelabend_14.09.2026.xlsx
@@ -893,13 +893,13 @@
         <v>Pünkt</v>
       </c>
       <c r="C23">
-        <v>5491</v>
+        <v>5550</v>
       </c>
       <c r="E23">
         <v>6885</v>
       </c>
       <c r="H23">
-        <v>-1394</v>
+        <v>-1335</v>
       </c>
     </row>
     <row r="24">
@@ -907,13 +907,13 @@
         <v>Runde 1</v>
       </c>
       <c r="C24">
-        <v>2700</v>
+        <v>2759</v>
       </c>
       <c r="E24">
         <v>3665</v>
       </c>
       <c r="H24">
-        <v>-965</v>
+        <v>-906</v>
       </c>
     </row>
     <row r="25">
@@ -1170,13 +1170,13 @@
         <v>Anteil Wiise an Total</v>
       </c>
       <c r="C38">
-        <v>0.145692952103442</v>
+        <v>0.14414414414414414</v>
       </c>
       <c r="E38">
         <v>0.23093681917211328</v>
       </c>
       <c r="H38">
-        <v>-0.36912202815585027</v>
+        <v>-0.3758286588475268</v>
       </c>
     </row>
     <row r="40">
